--- a/data/trans_orig/Q5407-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2007</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2170</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7232</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2170</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6642</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7286</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>49841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>58391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>74887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85846</t>
+          <t>86342</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,62 +1224,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51952</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63397</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>57398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>68275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>75395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89071</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39700</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222797</t>
+          <t>222836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241391</t>
+          <t>241260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>69035</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>80469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296659</t>
+          <t>297830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>319069</t>
+          <t>319684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>42889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>52617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60460</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79811</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108888</t>
+          <t>108910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129936</t>
+          <t>129332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30953</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39447</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67448</t>
+          <t>67660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66741</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>334931</t>
+          <t>335783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>366274</t>
+          <t>367413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>339001</t>
+          <t>339064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>370850</t>
+          <t>371915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>63840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>55136</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64499</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98609</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>102789</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142045</t>
+          <t>146733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>436682</t>
+          <t>435132</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>462462</t>
+          <t>462075</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>537075</t>
+          <t>537481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>576837</t>
+          <t>578079</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>984430</t>
+          <t>982755</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1030714</t>
+          <t>1029009</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2012</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>42890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55323</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>67062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>58473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72818</t>
+          <t>73147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93971</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111339</t>
+          <t>111239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33455</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133777</t>
+          <t>134132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154997</t>
+          <t>156168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>40848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49160</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167887</t>
+          <t>167920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>195197</t>
+          <t>194158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52866</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>212186</t>
+          <t>211170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243098</t>
+          <t>241914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55385</t>
+          <t>58580</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79695</t>
+          <t>80142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>94196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113160</t>
+          <t>112418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139638</t>
+          <t>138952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>199585</t>
+          <t>196190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229009</t>
+          <t>227915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>32117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>57689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32386</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57319</t>
+          <t>57667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65762</t>
+          <t>65403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>279460</t>
+          <t>284546</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316544</t>
+          <t>318788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285350</t>
+          <t>285791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320678</t>
+          <t>319272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71577</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109323</t>
+          <t>108868</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102075</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145577</t>
+          <t>148686</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>72759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84148</t>
+          <t>82860</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122261</t>
+          <t>119927</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>133157</t>
+          <t>135306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>181604</t>
+          <t>182010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>449764</t>
+          <t>450990</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>488342</t>
+          <t>487987</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>525269</t>
+          <t>525923</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>575653</t>
+          <t>573252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>990065</t>
+          <t>986010</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1051024</t>
+          <t>1051502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2016</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67166</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>35586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88322</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101667</t>
+          <t>101219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49792</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>50724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>63572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100461</t>
+          <t>99634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40144</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131471</t>
+          <t>131672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150506</t>
+          <t>150905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163991</t>
+          <t>164103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>182002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>68591</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87142</t>
+          <t>87352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>239946</t>
+          <t>239915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>264993</t>
+          <t>265649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>33472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41496</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63074</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105723</t>
+          <t>106147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124728</t>
+          <t>124831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>104239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128407</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216433</t>
+          <t>217918</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248278</t>
+          <t>247336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>87876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>87876</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289277</t>
+          <t>288697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>325844</t>
+          <t>327771</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289277</t>
+          <t>288697</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>325844</t>
+          <t>327771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41369</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73827</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>69755</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>109469</t>
+          <t>108156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>65481</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108917</t>
+          <t>110538</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155063</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>156957</t>
+          <t>158441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>208640</t>
+          <t>212331</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>492462</t>
+          <t>490224</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>523067</t>
+          <t>524113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>558120</t>
+          <t>557226</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>611150</t>
+          <t>610108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1061812</t>
+          <t>1058841</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1125854</t>
+          <t>1121036</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2023</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97211</t>
+          <t>97700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104753</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>62504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156518</t>
+          <t>156525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166103</t>
+          <t>166059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>81108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90153</t>
+          <t>89922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34581</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118418</t>
+          <t>118469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>129802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81749</t>
+          <t>81818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93133</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39421</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115295</t>
+          <t>115068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130352</t>
+          <t>130071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>50448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>22554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>51098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79025</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176600</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197682</t>
+          <t>196786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246368</t>
+          <t>246325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>319703</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>436749</t>
+          <t>437371</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>537165</t>
+          <t>537710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43982</t>
+          <t>43615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52818</t>
+          <t>53022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>39013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55323</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48501</t>
+          <t>48326</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67648</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67732</t>
+          <t>66871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79331</t>
+          <t>78535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112408</t>
+          <t>111744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131205</t>
+          <t>131650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184188</t>
+          <t>184528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207103</t>
+          <t>206972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49965</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>74022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54421</t>
+          <t>54509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74951</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>203995</t>
+          <t>203927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>228414</t>
+          <t>228219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204992</t>
+          <t>204171</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>230035</t>
+          <t>229163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30682</t>
+          <t>30954</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>49737</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123950</t>
+          <t>124244</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,47 +13797,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>134339</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>86781</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>159227</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>134339</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>88214</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>159327</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>46942</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69730</t>
+          <t>70472</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87610</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192965</t>
+          <t>192566</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>134816</t>
+          <t>138890</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>245376</t>
+          <t>243625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>525829</t>
+          <t>524413</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>554110</t>
+          <t>552661</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>702103</t>
+          <t>703787</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>870321</t>
+          <t>890623</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1254374</t>
+          <t>1256444</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1428450</t>
+          <t>1426414</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5407-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Clase-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49841</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58391</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>74737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86342</t>
+          <t>85978</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>52790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>63432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57398</t>
+          <t>57406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>67527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75395</t>
+          <t>76405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>88976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222836</t>
+          <t>222260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241260</t>
+          <t>241613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69035</t>
+          <t>67386</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80469</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297830</t>
+          <t>297014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>319684</t>
+          <t>319332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>43368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59786</t>
+          <t>61080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>79133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108910</t>
+          <t>108719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129332</t>
+          <t>129474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30654</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67660</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66271</t>
+          <t>68008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>335783</t>
+          <t>334796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>368075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>339064</t>
+          <t>336998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371915</t>
+          <t>371204</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36739</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>63621</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55136</t>
+          <t>53867</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102789</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>146733</t>
+          <t>141683</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>435132</t>
+          <t>435875</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>462075</t>
+          <t>461833</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>537481</t>
+          <t>535947</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>578079</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>982755</t>
+          <t>984509</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1029009</t>
+          <t>1031098</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67062</t>
+          <t>67101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>45742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58473</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58266</t>
+          <t>57241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73147</t>
+          <t>72500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95336</t>
+          <t>93863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111239</t>
+          <t>110973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134132</t>
+          <t>134397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156168</t>
+          <t>155226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>32519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>51847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167920</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194158</t>
+          <t>195103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,82 +5768,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>72,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>84,19%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>46538</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>39402</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>52262</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>77,44%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>65,57%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>228020</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>211468</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>241312</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>78,13%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>72,46%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46538</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>38914</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52560</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>77,44%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>64,75%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>228020</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>211170</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>241914</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46155</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58580</t>
+          <t>56988</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94196</t>
+          <t>94367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112418</t>
+          <t>111852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138952</t>
+          <t>138921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196190</t>
+          <t>198109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227915</t>
+          <t>229471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>32026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57689</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>57725</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65403</t>
+          <t>65096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>65935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>284546</t>
+          <t>281436</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>318788</t>
+          <t>315877</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285791</t>
+          <t>285723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>319272</t>
+          <t>320123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108868</t>
+          <t>107633</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>103332</t>
+          <t>103664</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>148686</t>
+          <t>147350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82860</t>
+          <t>85496</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119927</t>
+          <t>122977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135306</t>
+          <t>133194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>182010</t>
+          <t>183839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450990</t>
+          <t>449916</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>487987</t>
+          <t>487638</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>525923</t>
+          <t>525704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>573252</t>
+          <t>576916</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>986010</t>
+          <t>989908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1051502</t>
+          <t>1050604</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57114</t>
+          <t>59103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>67732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>88939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101219</t>
+          <t>101511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39477</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50724</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63572</t>
+          <t>63244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>26481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99634</t>
+          <t>100369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113455</t>
+          <t>113085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131672</t>
+          <t>132535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150905</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>45785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164103</t>
+          <t>163628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>182764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68591</t>
+          <t>69025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87352</t>
+          <t>87702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>239915</t>
+          <t>241713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>265649</t>
+          <t>266246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61476</t>
+          <t>61311</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106147</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124831</t>
+          <t>125183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104239</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>128647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>217918</t>
+          <t>219307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247336</t>
+          <t>249721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>48160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>48160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55449</t>
+          <t>54861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87876</t>
+          <t>90378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55449</t>
+          <t>54861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87876</t>
+          <t>90378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>288697</t>
+          <t>287835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>327771</t>
+          <t>328284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288697</t>
+          <t>287835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327771</t>
+          <t>328284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>44076</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>71990</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>69962</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108156</t>
+          <t>108035</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65481</t>
+          <t>63121</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110538</t>
+          <t>108658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>154278</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>157309</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>212331</t>
+          <t>208866</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490224</t>
+          <t>492349</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>524113</t>
+          <t>523682</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>557226</t>
+          <t>559743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>610108</t>
+          <t>611960</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1058841</t>
+          <t>1064968</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1121036</t>
+          <t>1122250</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>601</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -11119,22 +11119,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101857</t>
+          <t>114489</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97700</t>
+          <t>109660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>117490</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60018</t>
+          <t>68662</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>71695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>161875</t>
+          <t>183151</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156525</t>
+          <t>177089</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166059</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,22 +11532,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86246</t>
+          <t>95771</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81108</t>
+          <t>89772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89922</t>
+          <t>99470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>41193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41997</t>
+          <t>49349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>125069</t>
+          <t>141477</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118469</t>
+          <t>134466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129802</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88356</t>
+          <t>98222</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81818</t>
+          <t>92776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93038</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>31551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>123470</t>
+          <t>135832</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115068</t>
+          <t>126823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130071</t>
+          <t>143794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50448</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -12487,17 +12487,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51098</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>62101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188280</t>
+          <t>205964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177533</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>196786</t>
+          <t>217193</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>298508</t>
+          <t>100744</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246325</t>
+          <t>93411</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>319703</t>
+          <t>107226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>486788</t>
+          <t>306709</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437371</t>
+          <t>293606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>537710</t>
+          <t>318769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237466</t>
+          <t>259001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237466</t>
+          <t>259001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237466</t>
+          <t>259001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564159</t>
+          <t>389881</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564159</t>
+          <t>389881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564159</t>
+          <t>389881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43615</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35798</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53022</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46943</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>60870</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>56883</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48326</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>73084</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>82030</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>75819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>87919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122139</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111744</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131650</t>
+          <t>140408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>212231</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184528</t>
+          <t>198409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206972</t>
+          <t>223792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>204587</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204587</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204587</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296593</t>
+          <t>320458</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296593</t>
+          <t>320458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296593</t>
+          <t>320458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41193</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>56627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>62518</t>
+          <t>67604</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>79414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>69290</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54509</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74833</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>216416</t>
+          <t>231137</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>203927</t>
+          <t>216705</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>228219</t>
+          <t>245377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>217476</t>
+          <t>232209</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204171</t>
+          <t>218527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>229163</t>
+          <t>244943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>319637</t>
+          <t>343971</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>319637</t>
+          <t>343971</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>319637</t>
+          <t>343971</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>347247</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>347247</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>347247</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>39634</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49737</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>103987</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>90840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>124244</t>
+          <t>118559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>134339</t>
+          <t>144907</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86781</t>
+          <t>128313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159227</t>
+          <t>163383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46942</t>
+          <t>50488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70472</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>150234</t>
+          <t>164382</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192566</t>
+          <t>182490</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>208269</t>
+          <t>226571</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138890</t>
+          <t>206790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243625</t>
+          <t>249345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>539653</t>
+          <t>597550</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>524413</t>
+          <t>581192</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>552661</t>
+          <t>610782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>771018</t>
+          <t>614060</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>703787</t>
+          <t>592193</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>890623</t>
+          <t>632303</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1310671</t>
+          <t>1211609</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1256444</t>
+          <t>1186324</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426414</t>
+          <t>1236571</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>700659</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>700659</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>700659</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1015958</t>
+          <t>882429</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1015958</t>
+          <t>882429</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1015958</t>
+          <t>882429</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1653279</t>
+          <t>1583087</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1653279</t>
+          <t>1583087</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1653279</t>
+          <t>1583087</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
